--- a/data_extactor/batch_10_fa/trimmed/batch_0019_fa_trim.xlsx
+++ b/data_extactor/batch_10_fa/trimmed/batch_0019_fa_trim.xlsx
@@ -508,7 +508,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>نگارش | تفکر انتقادی | درک مطلب | شنیدن فعال | سخن گفتن | ریاضیات | نظارت | علوم پایه | یادگیری فعال | استراتژی‌های یادگیری</t>
+          <t>نگارش | تفکر انتقادی | درک مطلب | گوش دادن فعال | سخن گفتن | ریاضیات | نظارت | علوم | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -518,7 +518,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | استدلال قیاسی | بیان کتبی | حساسیت به مسئله | استدلال استقرایی | مرتب‌سازی اطلاعات</t>
+          <t>درک شفاهی | درک کتبی | استدلال قیاسی | بیان کتبی | حساسیت به مسئله | استدلال استقرایی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>مهندسان خودرو | مهندسان برق | تکنسین‌ها و کارشناسان ارشد مهندسی برق و الکترونیک | تکنسین‌ها و کارشناسان ارشد الکترومکانیک و مکاترونیک | مهندسان صنایع | مهندسان مکانیک | مهندسان رباتیک</t>
+          <t>مهندسان خودرو | مهندسان برق | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | کارشناسان و تکنسین‌های الکترومکانیک و مکاترونیک | مهندسان صنایع | مهندسان مکانیک | مهندسان رباتیک</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,7 +565,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | شنیدن فعال | درک مطلب | نگارش | سخن گفتن | علوم پایه | نظارت | یادگیری فعال | ریاضیات | استراتژی‌های یادگیری</t>
+          <t>تفکر انتقادی | گوش دادن فعال | درک مطلب | نگارش | سخن گفتن | علوم | نظارت | یادگیری فعال | ریاضیات | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -575,7 +575,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | بیان کتبی | مرتب‌سازی اطلاعات</t>
+          <t>درک شفاهی | درک کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | بیان کتبی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>مهندسان سخت‌افزار رایانه | مهندسان برق | مهندسان الکترونیک، به‌استثنای رایانه | دانشمندان علوم مواد | مهندسان مکانیک | مهندسان نانوسیستم‌ها | مهندسان فوتونیک</t>
+          <t>مهندسان سخت‌افزار رایانه | مهندسان برق | مهندسان الکترونیک، به‌جز کامپیوتر | کارشناسان و دانشمندان علوم مواد | مهندسان مکانیک | مهندسان نانوسیستم‌ها | مهندسان فوتونیک</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | نگارش | شنیدن فعال | ریاضیات | سخن گفتن | یادگیری فعال | علوم پایه | استراتژی‌های یادگیری | نظارت</t>
+          <t>تفکر انتقادی | درک مطلب | نگارش | گوش دادن فعال | ریاضیات | سخن گفتن | یادگیری فعال | علوم | راهبردهای یادگیری | نظارت</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | درک کتبی | درک شفاهی | استدلال ریاضی | حساسیت به مسئله</t>
+          <t>استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | درک کتبی | درک شفاهی | استدلال ریاضی | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>مهندسان برق | مهندسان الکترونیک، به‌استثنای رایانه | دانشمندان علوم مواد | مهندسان مکانیک | مهندسان میکروسیستم‌ها | مهندسان نانوسیستم‌ها | تکنسین‌های فوتونیک</t>
+          <t>مهندسان برق | مهندسان الکترونیک، به‌جز کامپیوتر | کارشناسان و دانشمندان علوم مواد | مهندسان مکانیک | مهندسان سامانه‌های میکرو / میکروسیستم‌ها | مهندسان نانوسیستم‌ها | تکنسین‌های فوتونیک و اپتیک</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | شنیدن فعال | نظارت | نگارش | ریاضیات | یادگیری فعال | استراتژی‌های یادگیری | سخن گفتن | علوم پایه</t>
+          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | نظارت | نگارش | ریاضیات | یادگیری فعال | راهبردهای یادگیری | سخن گفتن | علوم</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | درک شفاهی | درک کتبی | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | استدلال ریاضی</t>
+          <t>حساسیت به مسئله | درک شفاهی | درک کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>مهندسان سخت‌افزار رایانه | برنامه‌نویسان ماشین‌های ابزار CNC | مهندسان برق | مهندسان الکترونیک، به‌استثنای رایانه | مهندسان مکانیک | مهندسان مکاترونیک | تکنسین‌های رباتیک</t>
+          <t>مهندسان سخت‌افزار رایانه | برنامه‌نویسان ماشین‌ابزارهای کنترل عددی رایانه‌ای CNC | مهندسان برق | مهندسان الکترونیک، به‌جز کامپیوتر | مهندسان مکانیک | مهندسان مکاترونیک | تکنسین‌های رباتیک</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>سخن گفتن | درک مطلب | تفکر انتقادی | علوم پایه | شنیدن فعال | نگارش | ریاضیات | یادگیری فعال | نظارت | استراتژی‌های یادگیری</t>
+          <t>سخن گفتن | درک مطلب | تفکر انتقادی | علوم | گوش دادن فعال | نگارش | ریاضیات | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>استدلال قیاسی | استدلال استقرایی | درک شفاهی | درک کتبی | بیان کتبی | مرتب‌سازی اطلاعات | حساسیت به مسئله</t>
+          <t>استدلال قیاسی | استدلال استقرایی | درک شفاهی | درک کتبی | بیان کتبی | ترتیب‌دهی اطلاعات | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>مهندسان شیمی | شیمیدانان | مهندسان تولید و ساخت | مهندسان مواد | دانشمندان علوم مواد | مهندسان میکروسیستم‌ها | تکنسین‌ها و کارشناسان ارشد مهندسی نانوفناوری</t>
+          <t>مهندسان شیمی | شیمی‌دانان | مهندسان تولید و ساخت | مهندسان متالورژی و مواد | کارشناسان و دانشمندان علوم مواد | مهندسان سامانه‌های میکرو / میکروسیستم‌ها | کارشناسان و تکنسین‌های مهندسی نانوتکنولوژی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,12 +793,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | ریاضیات | شنیدن فعال | نگارش | سخن گفتن | علوم پایه | نظارت | یادگیری فعال</t>
+          <t>تفکر انتقادی | درک مطلب | ریاضیات | گوش دادن فعال | نگارش | سخن گفتن | علوم | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>مهندسی و فناوری | ریاضیات | طراحی | فیزیک | رایانه و الکترونیک | ساختمان و سازه | مکانیک</t>
+          <t>مهندسی و فناوری | ریاضیات | طراحی | فیزیک | رایانه و الکترونیک | ساختمان و ساخت‌وساز | مکانیک</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>مهندسان عمران | مهندسان برق | مهندسان انرژی، به‌استثنای باد و خورشید | مهندسان مکانیک | مهندسان سیستم‌های انرژی خورشیدی | مدیران توسعه انرژی باد | تکنسین‌های تعمیر و نگهداری توربین بادی</t>
+          <t>مهندسان عمران | مهندسان برق | مهندسان انرژی، به‌جز بادی و خورشیدی | مهندسان مکانیک | مهندسان سیستم‌های انرژی خورشیدی | مدیران توسعه پروژه‌های انرژی بادی | تکنسین‌های تعمیر و نگهداری توربین‌های بادی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,12 +850,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | نگارش | سخن گفتن | شنیدن فعال | ریاضیات | نظارت | یادگیری فعال | علوم پایه</t>
+          <t>تفکر انتقادی | درک مطلب | نگارش | سخن گفتن | گوش دادن فعال | ریاضیات | نظارت | یادگیری فعال | علوم</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>مهندسی و فناوری | طراحی | ساختمان و سازه | ریاضیات | مکانیک | فیزیک | رایانه و الکترونیک</t>
+          <t>مهندسی و فناوری | طراحی | ساختمان و ساخت‌وساز | ریاضیات | مکانیک | فیزیک | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>مهندسان برق | ممیزان انرژی | مهندسان انرژی، به‌استثنای باد و خورشید | مهندسان مکانیک | مدیران نصب سیستم‌های انرژی خورشیدی | نصابان سیستم‌های فتوولتائیک خورشیدی | نصابان و تکنسین‌های سیستم‌های خورشیدی حرارتی</t>
+          <t>مهندسان برق | ممیزان انرژی | مهندسان انرژی، به‌جز بادی و خورشیدی | مهندسان مکانیک | مدیران اجرای پروژه‌های انرژی خورشیدی | نصابان سیستم‌های خورشیدی فتوولتائیک | نصابان و تکنسین‌های سیستم‌های خورشیدی حرارتی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>درک مطلب | نگارش | تفکر انتقادی | یادگیری فعال | ریاضیات | شنیدن فعال | نظارت | سخن گفتن | استراتژی‌های یادگیری</t>
+          <t>درک مطلب | نگارش | تفکر انتقادی | یادگیری فعال | ریاضیات | گوش دادن فعال | نظارت | سخن گفتن | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>طراحی | ساختمان و سازه | مهندسی و فناوری | رایانه و الکترونیک | ریاضیات | ایمنی و امنیت عمومی</t>
+          <t>طراحی | ساختمان و ساخت‌وساز | مهندسی و فناوری | رایانه و الکترونیک | ریاضیات | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>تجسم فضایی | دید نزدیک | درک شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال ریاضی</t>
+          <t>تجسم | بینایی نزدیک | درک شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>معماران، به‌استثنای معماران منظر و طراحان شناورهای دریایی | تکنسین‌ها و کارشناسان ارشد مهندسی عمران | مهندسان عمران | مدیران پروژه‌های ساختمانی | نقشه‌کشان برق و الکترونیک | نقشه‌کشان مکانیک | تکنسین‌های نقشه‌برداری و نقشه‌نگاری</t>
+          <t>مهندسان معمار، به‌جز معماران منظر و سازه‌های دریایی | کارشناسان و تکنسین‌های مهندسی عمران | مهندسان عمران | مدیران پروژه‌های ساختمانی | نقشه‌کشان برق و الکترونیک | نقشه‌کشان مکانیک | تکنسین‌های نقشه‌برداری و نقشه‌نگاری</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>شنیدن فعال | نگارش | تفکر انتقادی | درک مطلب | یادگیری فعال | سخن گفتن | نظارت</t>
+          <t>گوش دادن فعال | نگارش | تفکر انتقادی | درک مطلب | یادگیری فعال | سخن گفتن | نظارت</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>درک کتبی | درک شفاهی | دید نزدیک | تجسم فضایی | بیان کتبی | مرتب‌سازی اطلاعات | استدلال قیاسی</t>
+          <t>درک کتبی | درک شفاهی | بینایی نزدیک | تجسم | بیان کتبی | ترتیب‌دهی اطلاعات | استدلال قیاسی</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>نقشه‌کشان معماری و عمران | مهندسان برق | تکنسین‌ها و کارشناسان ارشد مهندسی برق و الکترونیک | مونتاژکاران تجهیزات الکتریکی و الکترونیکی | مهندسان الکترونیک، به‌استثنای رایانه | نقشه‌کشان مکانیک | مهندسان مکاترونیک</t>
+          <t>نقشه‌کشان معماری و عمران | مهندسان برق | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | مونتاژکاران تجهیزات الکتریکی و الکترونیکی | مهندسان الکترونیک، به‌جز کامپیوتر | نقشه‌کشان مکانیک | مهندسان مکاترونیک</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | یادگیری فعال | ریاضیات | شنیدن فعال | درک مطلب | سخن گفتن | نگارش | نظارت</t>
+          <t>تفکر انتقادی | یادگیری فعال | ریاضیات | گوش دادن فعال | درک مطلب | سخن گفتن | نگارش | نظارت</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>دید نزدیک | تجسم فضایی | استدلال ریاضی | درک شفاهی | بیان کتبی | استدلال قیاسی | درک کتبی</t>
+          <t>بینایی نزدیک | تجسم | استدلال ریاضی | درک شفاهی | بیان کتبی | استدلال قیاسی | درک کتبی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>نقشه‌کشان معماری و عمران | برنامه‌نویسان ماشین‌های ابزار CNC | نقشه‌کشان برق و الکترونیک | مهندسان صنایع | ماشین‌کاران | تکنسین‌ها و کارشناسان ارشد مهندسی مکانیک | مهندسان مکانیک</t>
+          <t>نقشه‌کشان معماری و عمران | برنامه‌نویسان ماشین‌ابزارهای کنترل عددی رایانه‌ای CNC | نقشه‌کشان برق و الکترونیک | مهندسان صنایع | تراشکاران، فرزکاران و ماشین‌کاران قطعات دقیق | کارشناسان و تکنسین‌های مهندسی مکانیک | مهندسان مکانیک</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
